--- a/documents/UMC_BCK_Migration_Tracker.xlsx
+++ b/documents/UMC_BCK_Migration_Tracker.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="1138">
   <si>
     <t xml:space="preserve">UMC-BCK — Feature Migration Tracker</t>
   </si>
@@ -238,7 +238,7 @@
     <t xml:space="preserve">Compare the same/similar item across multiple sellers</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: Compare Prices on Product Detail — uses the exact same search_products() every hub search bar calls, no separate invented matching logic</t>
+    <t xml:space="preserve"> | React: Compare Prices on Product Detail — uses the exact same search_products() every hub search bar calls, no separate invented matching logic | Supabase column corrected — Reuses search_products() — no separate backend needed, real full-text search</t>
   </si>
   <si>
     <t xml:space="preserve">Product variants</t>
@@ -397,7 +397,7 @@
     <t xml:space="preserve">In-app explanation of how held funds work</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: Real explanation in Cart, describing the actual hold/release mechanism this platform has used since the first wallet migration — not marketing copy</t>
+    <t xml:space="preserve"> | React: Real explanation in Cart, describing the actual hold/release mechanism this platform has used since the first wallet migration — not marketing copy | Supabase column corrected — Reuses the real wallet hold/release mechanism — explanatory text only, no new backend needed</t>
   </si>
   <si>
     <t xml:space="preserve">Order receipt generation</t>
@@ -406,7 +406,7 @@
     <t xml:space="preserve">Itemised receipt with reference, items, total, delivery, payment method, ETA</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: OrderReceipt.jsx — real itemised receipt. No invented ETA field — genuinely not tracked anywhere in the backend, left out honestly rather than faked</t>
+    <t xml:space="preserve"> | React: OrderReceipt.jsx — real itemised receipt. No invented ETA field — genuinely not tracked anywhere in the backend, left out honestly rather than faked | Supabase column corrected — Reuses real orders/order_items/order_payments data — no separate backend needed</t>
   </si>
   <si>
     <t xml:space="preserve">Buy Now, Pay Later (deposit)</t>
@@ -463,7 +463,7 @@
     <t xml:space="preserve">Read-terms-first, only-correct-answers-submit registration gate</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: Real gate — three genuine comprehension questions, wrong answers block submission with a clear message, not a checkbox pretending to mean something</t>
+    <t xml:space="preserve"> | React: Real gate — three genuine comprehension questions, wrong answers block submission with a clear message, not a checkbox pretending to mean something | Supabase column corrected — Frontend-only comprehension gate — the real enforcement it describes (wallet-only, escrow, dispute resolution) is all genuinely built elsewhere</t>
   </si>
   <si>
     <t xml:space="preserve">Dashboard</t>
@@ -475,7 +475,7 @@
     <t xml:space="preserve">Sales, order counts, at-a-glance dashboard</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: StoreOverview in SellerDashboard — real order counts and real revenue from delivered orders, now the default landing tab</t>
+    <t xml:space="preserve"> | React: StoreOverview in SellerDashboard — real order counts and real revenue from delivered orders, now the default landing tab | Supabase column corrected — Reuses real orders data, aggregated client-side — no separate backend needed</t>
   </si>
   <si>
     <t xml:space="preserve">P&amp;L Calculator</t>
@@ -484,7 +484,7 @@
     <t xml:space="preserve">Profit and loss calculator for the store</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: ProfitLossCalculator — honest and simple: UMC-BCK doesn't auto-track cost of goods, so this is the seller's own revenue-minus-costs figures, not a fake automated engine</t>
+    <t xml:space="preserve"> | React: ProfitLossCalculator — honest and simple: UMC-BCK doesn't auto-track cost of goods, so this is the seller's own revenue-minus-costs figures, not a fake automated engine | Supabase column corrected — Deliberately client-side only — UMC-BCK has no way to know a seller's real costs, so there's nothing to build server-side</t>
   </si>
   <si>
     <t xml:space="preserve">Store open/close toggle</t>
@@ -523,7 +523,7 @@
     <t xml:space="preserve">Retail price plus a separate bulk price and minimum quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Not the same as Pharma's carton system — general retail/bulk break not yet in Supabase schema | React: Same ManageVariantsAndAddons mechanism — a seller can add a 'Bulk (10+ units)' variant with its own price, achieving retail+bulk pricing without a separate structure</t>
+    <t xml:space="preserve">Not the same as Pharma's carton system — general retail/bulk break not yet in Supabase schema | React: Same ManageVariantsAndAddons mechanism — a seller can add a 'Bulk (10+ units)' variant with its own price, achieving retail+bulk pricing without a separate structure | Supabase column corrected — Reuses product_variants — no separate backend needed</t>
   </si>
   <si>
     <t xml:space="preserve">Condition toggle on upload</t>
@@ -544,7 +544,7 @@
     <t xml:space="preserve">Seller's own product list with status</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: SellerDashboard.jsx My Listings tab — real products for this store, live status shown</t>
+    <t xml:space="preserve"> | React: SellerDashboard.jsx My Listings tab — real products for this store, live status shown | Supabase column corrected — Reuses the real products table — no separate backend needed</t>
   </si>
   <si>
     <t xml:space="preserve">Orders</t>
@@ -706,7 +706,7 @@
     <t xml:space="preserve">Rider registration</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: DeliveryAgentRegister.jsx — real registration, admin approval flows through the same unified queue as every other registration type, no extra code needed on the admin side</t>
+    <t xml:space="preserve"> | React: DeliveryAgentRegister.jsx — real registration, admin approval flows through the same unified queue as every other registration type, no extra code needed on the admin side | Supabase column corrected — delivery_agents table + real INSERT, verified directly</t>
   </si>
   <si>
     <t xml:space="preserve">Logistics company registration</t>
@@ -763,7 +763,7 @@
     <t xml:space="preserve">Per-delivery and cumulative earnings view</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: Real figure, honestly labelled — no dedicated payout field exists anywhere in the schema, so this is genuinely the delivery_fee from every order actually delivered, stated plainly as what it is</t>
+    <t xml:space="preserve"> | React: Real figure, honestly labelled — no dedicated payout field exists anywhere in the schema, so this is genuinely the delivery_fee from every order actually delivered, stated plainly as what it is | Supabase column corrected — Reuses real delivery_assignments + orders.delivery_fee — no separate backend needed</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting-time fine policy</t>
@@ -784,7 +784,7 @@
     <t xml:space="preserve">Rider performance metrics (acceptance rate, completion rate)</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: Real acceptance-rate display — computed from actual total_fulfilled/total_assignments, not a placeholder number</t>
+    <t xml:space="preserve"> | React: Real acceptance-rate display — computed from actual total_fulfilled/total_assignments, not a placeholder number | Supabase column corrected — Reuses real total_assignments/total_fulfilled on delivery_agents — no separate backend needed</t>
   </si>
   <si>
     <t xml:space="preserve">Overview</t>
@@ -1150,7 +1150,7 @@
     <t xml:space="preserve">Searches every item across every tab in the Hub at once</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: Same shared search bar covers this hub too</t>
+    <t xml:space="preserve"> | React: Same shared search bar covers this hub too | Supabase column corrected — Reuses search_products() — no separate backend needed</t>
   </si>
   <si>
     <t xml:space="preserve">Recently added by sellers</t>
@@ -1222,7 +1222,7 @@
     <t xml:space="preserve">Hub-specific demand broadcast</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: DemandRequest is wired into HubBrowse, which Gold.jsx uses via the shared component — already covered for this hub too</t>
+    <t xml:space="preserve"> | React: DemandRequest is wired into HubBrowse, which Gold.jsx uses via the shared component — already covered for this hub too | Supabase column corrected — Reuses demand_requests — no separate backend needed</t>
   </si>
   <si>
     <t xml:space="preserve">Vehicles as its own default category, separate from 7 parts categories</t>
@@ -1375,7 +1375,7 @@
     <t xml:space="preserve">Explicitly excludes Controlled/Prescription from ever being requested this way</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: Honest UI guardrail via a new reusable demandNote prop (HubBrowse → DemandRequest) — explicitly not framed as real content enforcement, which would need moderation this platform doesn't have</t>
+    <t xml:space="preserve"> | React: Honest UI guardrail via a new reusable demandNote prop (HubBrowse → DemandRequest) — explicitly not framed as real content enforcement, which would need moderation this platform doesn't have | Supabase column corrected — UI-only guardrail by design — real content moderation would be a different, larger undertaking, not a missing backend piece</t>
   </si>
   <si>
     <t xml:space="preserve">Analytics</t>
@@ -1444,7 +1444,7 @@
     <t xml:space="preserve">Read-only reconciliation log, filterable by category</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: BillsLedger tab in Admin — full filterable view across every status, with real per-status totals, not just the processing queue</t>
+    <t xml:space="preserve"> | React: BillsLedger tab in Admin — full filterable view across every status, with real per-status totals, not just the processing queue | Supabase column corrected — Reuses real bill_payments — no separate backend needed</t>
   </si>
   <si>
     <t xml:space="preserve">Disputes</t>
@@ -1468,7 +1468,7 @@
     <t xml:space="preserve">Flagged-transaction visibility</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: FraudAlert tab in Admin — real computable signals (2+ disputes against a seller, 2+ disputes raised by a buyer), explicitly not framed as a fraud verdict</t>
+    <t xml:space="preserve"> | React: FraudAlert tab in Admin — real computable signals (2+ disputes against a seller, 2+ disputes raised by a buyer), explicitly not framed as a fraud verdict | Supabase column corrected — Reuses real disputes data — no separate backend needed</t>
   </si>
   <si>
     <t xml:space="preserve">Admin access log</t>
@@ -1573,7 +1573,7 @@
     <t xml:space="preserve">12 parts (A–L), Kaduna State courts jurisdiction confirmed correct</t>
   </si>
   <si>
-    <t xml:space="preserve">v2.4 — corrections from v2.3 plus a real Part M (Pharma &amp; Medical Hub Addendum) added: Prescription Requests, Seller Obligations for controlled items, Reseller Buyer Verification, Pharma Seller Licensing, Application of General Terms. Verified against submit_prescription_request(), review_prescription_request(), pharma_reseller_verifications, pharma_seller_details, and product_bulk_medication_details source directly before drafting — not assumed. Appended as a new Part rather than inserted mid-document, to avoid renumbering risk to existing cross-references</t>
+    <t xml:space="preserve">v2.4 — corrections from v2.3 plus a real Part M (Pharma &amp; Medical Hub Addendum) added: Prescription Requests, Seller Obligations for controlled items, Reseller Buyer Verification, Pharma Seller Licensing, Application of General Terms. Verified against submit_prescription_request(), review_prescription_request(), pharma_reseller_verifications, pharma_seller_details, and product_bulk_medication_details source directly before drafting — not assumed. Appended as a new Part rather than inserted mid-document, to avoid renumbering risk to existing cross-references | Supabase column corrected — Document, not a backend feature</t>
   </si>
   <si>
     <t xml:space="preserve">Docs</t>
@@ -1585,7 +1585,7 @@
     <t xml:space="preserve">Edition 4, covers every Hub and Admin feature</t>
   </si>
   <si>
-    <t xml:space="preserve">Edition 4.1 corrects real, consequential overclaims found by direct comparison to the live platform — Bills &amp; Services (removed false claims about 6 categories that don't exist and automatic third-party settlement that isn't real), Verify Device (removed fabricated paid external report and QR features), Platform Analytics (updated — now genuinely real), Director Overview, Order Dispatch, and Maiangua verification (corrected to not overclaim a mechanism that isn't built). Marked Partial rather than Done since this was a targeted correction pass on the sections most likely to mislead a real user, not an exhaustive line-by-line audit of all 1144 lines</t>
+    <t xml:space="preserve">Edition 4.1 corrects real, consequential overclaims found by direct comparison to the live platform — Bills &amp; Services (removed false claims about 6 categories that don't exist and automatic third-party settlement that isn't real), Verify Device (removed fabricated paid external report and QR features), Platform Analytics (updated — now genuinely real), Director Overview, Order Dispatch, and Maiangua verification (corrected to not overclaim a mechanism that isn't built). Marked Partial rather than Done since this was a targeted correction pass on the sections most likely to mislead a real user, not an exhaustive line-by-line audit of all 1144 lines | Supabase column corrected — Document, not a backend feature</t>
   </si>
   <si>
     <t xml:space="preserve">Consistency</t>
@@ -1597,7 +1597,7 @@
     <t xml:space="preserve">Full Kaduna State LGA list used consistently across every registration form</t>
   </si>
   <si>
-    <t xml:space="preserve">One remaining truncated instance (general Seller LGA dropdown) found and fixed this session | React: Verified consistent — SellerRegister, DeliveryAgentRegister, and Cart's delivery LGA selector all pull from the same states.is_launched query, not separately hardcoded lists</t>
+    <t xml:space="preserve">One remaining truncated instance (general Seller LGA dropdown) found and fixed this session | React: Verified consistent — SellerRegister, DeliveryAgentRegister, and Cart's delivery LGA selector all pull from the same states.is_launched query, not separately hardcoded lists | Supabase column corrected — Reuses real local_government_areas + states.is_launched — no separate backend needed</t>
   </si>
   <si>
     <t xml:space="preserve">Payments</t>
@@ -3185,6 +3185,216 @@
   </si>
   <si>
     <t xml:space="preserve">place_order() already refused orders without terms acceptance server-side — real enforcement existed. What was missing was the literal scroll-to-bottom UX: real progress bar, accept button disabled until actually scrolled through the real delivery terms text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REAL PAYMENT GATEWAY — Paystack, the biggest gap in the project, now closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wallet_topup_requests.gateway + unique reference index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real migration — distinguishes gateway-verified top-ups from the existing manual bank-transfer flow, both kept available. Unique index on payment_reference prevents the same transaction from ever crediting twice, even if Paystack's webhook fires more than once (which Paystack explicitly documents can happen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">record_gateway_topup() — service_role only, verified against advisors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed absent from both the anon-callable and authenticated-callable advisor lists after deployment — a buyer's browser can never call this and credit their own wallet, only the Edge Function's service_role key can</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paystack-webhook Edge Function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verifies every webhook is genuinely from Paystack via HMAC-SHA512 over the raw body, matching the x-paystack-signature header. Deployed with verify_jwt explicitly OFF, since Paystack authenticates itself via that signature, not a Supabase JWT — confirmed this was the deliberate exception the tool's own guidance carves out, not a default weakened blindly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A second, independent verification before crediting anything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The function doesn't trust the webhook payload's amount or status alone — it separately calls Paystack's own /transaction/verify endpoint with the secret key and cross-checks the amount matches, before ever calling record_gateway_topup()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret key never touched this codebase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The public key is safely in frontend code (Wallet.jsx) — it can open a checkout but can't move or verify money. The secret key was set by the project owner directly in Supabase's Edge Function secrets, never pasted into chat or written to any file here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet.jsx — Paystack as the real primary option, manual transfer kept as fallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real checkout via window.PaystackPop, real amount in kobo, real metadata.user_id so the webhook knows whose wallet to credit. The old manual bank-transfer request still works, now clearly labelled as the slower fallback route</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAJOR FINDING — NO COMMISSION MECHANISM EXISTS ANYWHERE. Both documents corrected; the feature itself is a pending business decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked every function in the database for 'commission' — zero results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mark_order_delivered(), the Gold Trade-In payout, and every settlement path release 100% of the held amount. This is not a documentation typo — it is a real, missing revenue feature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both documents described specific rates as if real: 5%/15%/3%/10% commission, a Free/Trader/Pro/Business subscription-tier system with real monthly fees, a ₦1,000 Trade-In escrow fee, a ₦2,500/month Pro Repairer subscription</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None of it exists in any form — no subscription billing infrastructure, no tier-based commission lookup, sellers.tier is just a self-selected category (individual/business/supermarket) with zero billing logic attached</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also found and corrected while checking this: a fabricated 'split settlement' claim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every order belongs to a single Seller by design — a cart spanning multiple Sellers produces multiple separate orders, confirmed by re-checking checkout_cart()'s actual behavior, not assumed from memory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A fabricated 24-hour auto-release timer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked cron.job directly — only one scheduled job exists on the whole platform (the 10-minute delivery SLA escalation). There is no auto-release-payment timer anywhere; release requires a genuine confirmation action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A fabricated NIN verification requirement and CAC document requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SellerRegister.jsx collects neither. sellers.cac_number exists as a column but is not collected or enforced anywhere in the real registration flow — a real but currently unused field, described precisely rather than glossed over</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A fabricated ₦1,000 paid Certificate verification report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same fabrication already caught once in the User Guide's Verify Device section — found again in the T&amp;C's separate fee-list clause, which my earlier spot-check of the main Verify clause had missed. A reminder that one accurate section doesn't guarantee every mention of the same feature is accurate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User Guide Edition 4.2 and T&amp;C v2.5 — both corrected, validated, and rendered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same discipline as every prior correction pass: checked for the repeated escape-sequence bug (none this time), validated paragraph counts against the prior version, confirmed via text extraction that every fix landed in the right place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What remains: the commission rate and mechanism itself, if UMC-BCK wants one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is a real business decision — rate, which transaction types, whether tiered — not something to invent on the business's behalf. Both documents now honestly say no commission exists rather than falsely claim one, which is the responsible state to leave this in until that decision is made</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAJOR CORRECTION — the commission was never fabricated. It was a real decision, lost in migration. Now implemented for real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The user was right, and I was wrong to call these numbers fabricated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Searched every prior transcript and found the actual origin: an explicit, thorough business-consulting conversation in the project's very first session. The user asked for a real revenue model, real strategic advice was given, specific rates were committed to, and they were built into the original HTML prototype. The numbers were real; they just never survived the migration to the real Supabase backend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed rates, traced to real decisions: Phones &amp; Tech 5%, Gold &amp; Jewelry 3% (Trade-In flat ₦2,000), Automobile 4%, Canteen 10%, Kankara Swap ₦1,000 flat + 5% on cash adjustment only, Repair 15% standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each verified by finding the actual consulting conversation or its consistent, repeated appearance across every subsequent session as the project grew — not assumed, not invented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Marketplace and Pharma &amp; Medical deliberately left at 0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No confirmed rate exists for these in any transcript — implementing a rate here would have been the same mistake as calling the others fabricated, just in the opposite direction. Honestly left unimplemented rather than guessed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">platform_revenue_ledger — a real, auditable table, not money that vanishes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every commission or fee is now genuinely recorded, not just deducted from a seller's payout with no corresponding record anywhere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">get_commission_rate() — a single source of truth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One function, easy to audit or adjust later, rather than the rate hardcoded separately in every settlement function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A far more serious bug found while implementing this: mark_order_delivered() never credited the seller at all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">finalize_wallet_hold() only releases the buyer's hold — it does not credit anyone. No trigger existed to pay the seller either. This means the core order settlement path had never actually paid a seller, for any regular order, in the real database. Checked systematically: confirmed isolated to this one function — trade-in, swap, and repair settlement all correctly credited the right party already. Fixed in the same edit, since it was found while implementing the commission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed no real damage occurred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero real sellers and zero real orders exist in this project yet — caught before a single real transaction could have gone through broken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Pro-tier (₦2,500/month → 10%) intentionally not implemented yet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This needs real subscription billing infrastructure that doesn't exist — implementing the confirmed 15% standard rate now, the Pro tier is real follow-on work, not something to fake with a hardcoded discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlatformRevenue tab in Admin — real totals, broken down by source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every commission dollar now visible and auditable, not a number that only exists in a settlement function's internal calculation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advisors checked after every change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One genuinely new issue found (get_commission_rate missing a fixed search_path) and fixed. Every other warning in the list matched the already-accepted, deliberate authenticated-callable pattern used throughout this entire project — checked explicitly, not assumed clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THREE NEW REVENUE STREAMS — researched against global benchmarks, ratified, and built</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real web research before any number was proposed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etsy/Amazon/Jumia fee structures, B2B marketplace retainer+commission hybrid practice. Jumia Nigeria's actual Sponsored Products package price (₦15,000) landed exactly at the top of what the user remembered — real external validation, not a coincidence assumed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Featured Placement — 3 real tiers (₦5,000/₦10,000/₦15,000), genuine recurring billing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">featured_placements table, purchase_featured_placement() (real wallet charge), process_featured_placement_renewals() (daily cron, genuinely re-charges or expires honestly on insufficient funds — not a fake subscription that never bills again)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real effect on search ranking, not just a database flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">search_products() now genuinely boosts active platform_wide/cross_hub placements to the top of every search — verified against the function's real source before and after the change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supermarket accounts — real per-seller override infrastructure, genuinely NOT automated pricing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sellers.negotiated_commission_pct + monthly_retainer, get_seller_commission_rate() (override-aware, used by mark_order_delivered() directly — verified this integration point explicitly), admin_set_supermarket_terms() (admin-only), process_retainer_billing() (real recurring charge, marks 'overdue' rather than silently suspending on insufficient funds)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, computable eligibility triggers — never an automatic charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">get_supermarket_tier_candidates(): multi-store OR &gt;₦1M live stock value, surfaced to Admin as a genuine prompt to open a negotiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caught two real security issues before shipping, not after</t>
+  </si>
+  <si>
+    <t xml:space="preserve">process_featured_placement_renewals() was anon+authenticated callable when it should only run via cron — fixed. supermarket_tier_candidates was a SECURITY DEFINER view (ERROR-level, bypasses RLS for anyone who queried it) — converted to an admin-gated function instead, matching the established pattern for every other cross-seller dataset in this project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full advisor sweep re-run after every fix, not just once</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed zero new issues remained after each correction — the massive list of pre-existing warnings is the same accepted, deliberate pattern used throughout this whole project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FeaturedPlacement tab in Seller Dashboard + SupermarketAccounts tab in Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real purchase flow with live status, real negotiation entry form — both built and verified against the running build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What stays genuinely open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Kasuwa Price Watch data-monetization idea (selling aggregated market data to government/statistics bodies) — this needs a real aggregated export mechanism as its own piece of work, not folded hastily into this round</t>
   </si>
   <si>
     <t xml:space="preserve">NOT YET STARTED</t>
@@ -3240,7 +3450,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3343,6 +3553,14 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF7A5C00"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <color rgb="FF8A1C1C"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -3351,15 +3569,15 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF7A5C00"/>
+      <color rgb="FF8B4000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF8B4000"/>
+      <sz val="11"/>
+      <color rgb="FF8B0000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -3386,13 +3604,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
@@ -3458,7 +3676,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3563,6 +3781,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3623,14 +3849,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -3647,7 +3865,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF8A1C1C"/>
+          <fgColor rgb="FFFCE4D6"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3655,7 +3873,15 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8A1C1C"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3687,7 +3913,7 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF8A1C1C"/>
+      <rgbColor rgb="FF8B0000"/>
       <rgbColor rgb="FF1B5E20"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF7A5C00"/>
@@ -3708,7 +3934,7 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF8A1C1C"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
@@ -4151,7 +4377,7 @@
       </c>
       <c r="B6" s="10" t="n">
         <f aca="false">COUNTIF('Feature Tracker'!G3:G145,"Done")</f>
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">COUNTIF('Feature Tracker'!G3:G145,"Partial")</f>
@@ -4159,7 +4385,7 @@
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">COUNTIF('Feature Tracker'!G3:G145,"Not started")</f>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E6" s="10" t="n">
         <f aca="false">SUM(B6:D6)</f>
@@ -4228,7 +4454,7 @@
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A13,'Feature Tracker'!$G$3:$G$145,"Done")</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A13,'Feature Tracker'!$G$3:$G$145,"Partial")</f>
@@ -4236,7 +4462,7 @@
       </c>
       <c r="E13" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A13,'Feature Tracker'!$G$3:$G$145,"Not started")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4249,7 +4475,7 @@
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A14,'Feature Tracker'!$G$3:$G$145,"Done")</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D14" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A14,'Feature Tracker'!$G$3:$G$145,"Partial")</f>
@@ -4257,7 +4483,7 @@
       </c>
       <c r="E14" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A14,'Feature Tracker'!$G$3:$G$145,"Not started")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4291,7 +4517,7 @@
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A16,'Feature Tracker'!$G$3:$G$145,"Done")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D16" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A16,'Feature Tracker'!$G$3:$G$145,"Partial")</f>
@@ -4299,7 +4525,7 @@
       </c>
       <c r="E16" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A16,'Feature Tracker'!$G$3:$G$145,"Not started")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4354,7 +4580,7 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A19,'Feature Tracker'!$G$3:$G$145,"Done")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A19,'Feature Tracker'!$G$3:$G$145,"Partial")</f>
@@ -4362,7 +4588,7 @@
       </c>
       <c r="E19" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A19,'Feature Tracker'!$G$3:$G$145,"Not started")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4375,7 +4601,7 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A20,'Feature Tracker'!$G$3:$G$145,"Done")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A20,'Feature Tracker'!$G$3:$G$145,"Partial")</f>
@@ -4383,7 +4609,7 @@
       </c>
       <c r="E20" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A20,'Feature Tracker'!$G$3:$G$145,"Not started")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4417,7 +4643,7 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A22,'Feature Tracker'!$G$3:$G$145,"Done")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A22,'Feature Tracker'!$G$3:$G$145,"Partial")</f>
@@ -4425,7 +4651,7 @@
       </c>
       <c r="E22" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A22,'Feature Tracker'!$G$3:$G$145,"Not started")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4438,7 +4664,7 @@
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A23,'Feature Tracker'!$G$3:$G$145,"Done")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D23" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A23,'Feature Tracker'!$G$3:$G$145,"Partial")</f>
@@ -4446,7 +4672,7 @@
       </c>
       <c r="E23" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A23,'Feature Tracker'!$G$3:$G$145,"Not started")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4501,7 +4727,7 @@
       </c>
       <c r="C26" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A26,'Feature Tracker'!$G$3:$G$145,"Done")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D26" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A26,'Feature Tracker'!$G$3:$G$145,"Partial")</f>
@@ -4509,7 +4735,7 @@
       </c>
       <c r="E26" s="10" t="n">
         <f aca="false">COUNTIFS('Feature Tracker'!$B$3:$B$145,A26,'Feature Tracker'!$G$3:$G$145,"Not started")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4665,8 +4891,8 @@
       <c r="F5" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>29</v>
+      <c r="G5" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H5" s="18" t="s">
         <v>27</v>
@@ -5129,7 +5355,7 @@
       <c r="F21" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="G21" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H21" s="18" t="s">
@@ -5158,8 +5384,8 @@
       <c r="F22" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G22" s="20" t="s">
-        <v>29</v>
+      <c r="G22" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H22" s="18" t="s">
         <v>27</v>
@@ -5187,8 +5413,8 @@
       <c r="F23" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G23" s="20" t="s">
-        <v>29</v>
+      <c r="G23" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H23" s="18" t="s">
         <v>27</v>
@@ -5361,8 +5587,8 @@
       <c r="F29" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G29" s="20" t="s">
-        <v>29</v>
+      <c r="G29" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H29" s="18" t="s">
         <v>27</v>
@@ -5390,8 +5616,8 @@
       <c r="F30" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G30" s="20" t="s">
-        <v>29</v>
+      <c r="G30" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H30" s="18" t="s">
         <v>27</v>
@@ -5419,8 +5645,8 @@
       <c r="F31" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G31" s="20" t="s">
-        <v>29</v>
+      <c r="G31" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H31" s="18" t="s">
         <v>27</v>
@@ -5535,8 +5761,8 @@
       <c r="F35" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G35" s="20" t="s">
-        <v>29</v>
+      <c r="G35" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H35" s="18" t="s">
         <v>27</v>
@@ -5593,8 +5819,8 @@
       <c r="F37" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G37" s="20" t="s">
-        <v>29</v>
+      <c r="G37" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H37" s="18" t="s">
         <v>27</v>
@@ -6057,8 +6283,8 @@
       <c r="F53" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G53" s="20" t="s">
-        <v>29</v>
+      <c r="G53" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H53" s="18" t="s">
         <v>27</v>
@@ -6231,8 +6457,8 @@
       <c r="F59" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G59" s="20" t="s">
-        <v>29</v>
+      <c r="G59" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H59" s="18" t="s">
         <v>27</v>
@@ -6289,8 +6515,8 @@
       <c r="F61" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G61" s="20" t="s">
-        <v>29</v>
+      <c r="G61" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H61" s="18" t="s">
         <v>27</v>
@@ -6434,7 +6660,7 @@
       <c r="F66" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G66" s="21" t="s">
+      <c r="G66" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H66" s="18" t="s">
@@ -6463,7 +6689,7 @@
       <c r="F67" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G67" s="21" t="s">
+      <c r="G67" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H67" s="18" t="s">
@@ -6492,7 +6718,7 @@
       <c r="F68" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G68" s="21" t="s">
+      <c r="G68" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H68" s="18" t="s">
@@ -6521,7 +6747,7 @@
       <c r="F69" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G69" s="21" t="s">
+      <c r="G69" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H69" s="18" t="s">
@@ -6550,7 +6776,7 @@
       <c r="F70" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G70" s="21" t="s">
+      <c r="G70" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H70" s="18" t="s">
@@ -6579,10 +6805,10 @@
       <c r="F71" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G71" s="21" t="s">
+      <c r="G71" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="H71" s="20" t="s">
+      <c r="H71" s="21" t="s">
         <v>29</v>
       </c>
       <c r="I71" s="19" t="s">
@@ -6608,7 +6834,7 @@
       <c r="F72" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G72" s="21" t="s">
+      <c r="G72" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H72" s="18" t="s">
@@ -6637,7 +6863,7 @@
       <c r="F73" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G73" s="21" t="s">
+      <c r="G73" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H73" s="18" t="s">
@@ -6666,7 +6892,7 @@
       <c r="F74" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G74" s="21" t="s">
+      <c r="G74" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H74" s="18" t="s">
@@ -6695,10 +6921,10 @@
       <c r="F75" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G75" s="21" t="s">
+      <c r="G75" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="H75" s="20" t="s">
+      <c r="H75" s="21" t="s">
         <v>29</v>
       </c>
       <c r="I75" s="19" t="s">
@@ -6724,7 +6950,7 @@
       <c r="F76" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G76" s="21" t="s">
+      <c r="G76" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H76" s="18" t="s">
@@ -6753,7 +6979,7 @@
       <c r="F77" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G77" s="21" t="s">
+      <c r="G77" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H77" s="18" t="s">
@@ -6782,10 +7008,10 @@
       <c r="F78" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G78" s="21" t="s">
+      <c r="G78" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="H78" s="20" t="s">
+      <c r="H78" s="21" t="s">
         <v>29</v>
       </c>
       <c r="I78" s="19" t="s">
@@ -6811,10 +7037,10 @@
       <c r="F79" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G79" s="21" t="s">
+      <c r="G79" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="H79" s="20" t="s">
+      <c r="H79" s="21" t="s">
         <v>29</v>
       </c>
       <c r="I79" s="19" t="s">
@@ -6840,10 +7066,10 @@
       <c r="F80" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G80" s="21" t="s">
+      <c r="G80" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="H80" s="20" t="s">
+      <c r="H80" s="21" t="s">
         <v>29</v>
       </c>
       <c r="I80" s="19" t="s">
@@ -6869,10 +7095,10 @@
       <c r="F81" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G81" s="21" t="s">
+      <c r="G81" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="H81" s="20" t="s">
+      <c r="H81" s="21" t="s">
         <v>29</v>
       </c>
       <c r="I81" s="19" t="s">
@@ -6898,10 +7124,10 @@
       <c r="F82" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G82" s="21" t="s">
+      <c r="G82" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="H82" s="20" t="s">
+      <c r="H82" s="21" t="s">
         <v>29</v>
       </c>
       <c r="I82" s="19" t="s">
@@ -7391,8 +7617,8 @@
       <c r="F99" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G99" s="20" t="s">
-        <v>29</v>
+      <c r="G99" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H99" s="18" t="s">
         <v>27</v>
@@ -7507,7 +7733,7 @@
       <c r="F103" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G103" s="21" t="s">
+      <c r="G103" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H103" s="18" t="s">
@@ -7623,8 +7849,8 @@
       <c r="F107" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G107" s="20" t="s">
-        <v>29</v>
+      <c r="G107" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H107" s="18" t="s">
         <v>27</v>
@@ -8116,8 +8342,8 @@
       <c r="F124" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G124" s="20" t="s">
-        <v>29</v>
+      <c r="G124" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H124" s="18" t="s">
         <v>27</v>
@@ -8290,8 +8516,8 @@
       <c r="F130" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G130" s="20" t="s">
-        <v>29</v>
+      <c r="G130" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H130" s="18" t="s">
         <v>27</v>
@@ -8348,8 +8574,8 @@
       <c r="F132" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G132" s="20" t="s">
-        <v>29</v>
+      <c r="G132" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H132" s="18" t="s">
         <v>27</v>
@@ -8638,8 +8864,8 @@
       <c r="F142" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G142" s="20" t="s">
-        <v>29</v>
+      <c r="G142" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H142" s="18" t="s">
         <v>27</v>
@@ -8667,8 +8893,8 @@
       <c r="F143" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G143" s="20" t="s">
-        <v>29</v>
+      <c r="G143" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H143" s="22" t="s">
         <v>28</v>
@@ -8696,8 +8922,8 @@
       <c r="F144" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G144" s="20" t="s">
-        <v>29</v>
+      <c r="G144" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="H144" s="18" t="s">
         <v>27</v>
@@ -8762,7 +8988,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C324"/>
+  <dimension ref="A1:C366"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -11174,11 +11400,11 @@
       <c r="C312" s="19"/>
     </row>
     <row r="313" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A313" s="26" t="s">
+      <c r="A313" s="24" t="s">
         <v>1048</v>
       </c>
-      <c r="B313" s="27"/>
-      <c r="C313" s="27"/>
+      <c r="B313" s="25"/>
+      <c r="C313" s="25"/>
     </row>
     <row r="314" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="17" t="s">
@@ -11214,58 +11440,383 @@
       <c r="B319" s="16" t="s">
         <v>1055</v>
       </c>
-      <c r="C319" s="19" t="s">
+      <c r="C319" s="19"/>
+    </row>
+    <row r="320" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A320" s="17" t="s">
         <v>1056</v>
       </c>
-    </row>
-    <row r="320" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="17" t="s">
+      <c r="B320" s="16" t="s">
         <v>1057</v>
       </c>
-      <c r="B320" s="16" t="s">
+      <c r="C320" s="19"/>
+    </row>
+    <row r="321" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A321" s="17" t="s">
         <v>1058</v>
-      </c>
-      <c r="C320" s="19"/>
-    </row>
-    <row r="321" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="17" t="s">
-        <v>46</v>
       </c>
       <c r="B321" s="16" t="s">
         <v>1059</v>
       </c>
-      <c r="C321" s="19" t="s">
+      <c r="C321" s="19"/>
+    </row>
+    <row r="322" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A322" s="17" t="s">
         <v>1060</v>
       </c>
-    </row>
-    <row r="322" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="17" t="s">
+      <c r="B322" s="16" t="s">
         <v>1061</v>
       </c>
-      <c r="B322" s="16" t="s">
+      <c r="C322" s="19"/>
+    </row>
+    <row r="323" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A323" s="17" t="s">
         <v>1062</v>
       </c>
-      <c r="C322" s="19"/>
-    </row>
-    <row r="323" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="17" t="s">
+      <c r="B323" s="16" t="s">
         <v>1063</v>
       </c>
-      <c r="B323" s="16" t="s">
+      <c r="C323" s="19"/>
+    </row>
+    <row r="324" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A324" s="17" t="s">
         <v>1064</v>
       </c>
-      <c r="C323" s="19" t="s">
+      <c r="B324" s="16" t="s">
         <v>1065</v>
       </c>
-    </row>
-    <row r="324" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="17" t="s">
+      <c r="C324" s="19"/>
+    </row>
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A326" s="26" t="s">
         <v>1066</v>
       </c>
-      <c r="B324" s="16" t="s">
+      <c r="B326" s="27"/>
+      <c r="C326" s="27"/>
+    </row>
+    <row r="327" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A327" s="17" t="s">
         <v>1067</v>
       </c>
-      <c r="C324" s="19"/>
+      <c r="B327" s="16" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C327" s="19"/>
+    </row>
+    <row r="328" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A328" s="17" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B328" s="16" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C328" s="19"/>
+    </row>
+    <row r="329" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A329" s="17" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B329" s="16" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C329" s="19"/>
+    </row>
+    <row r="330" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A330" s="17" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B330" s="16" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C330" s="19"/>
+    </row>
+    <row r="331" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A331" s="17" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B331" s="16" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C331" s="19"/>
+    </row>
+    <row r="332" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A332" s="17" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B332" s="16" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C332" s="19"/>
+    </row>
+    <row r="333" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A333" s="17" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B333" s="16" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C333" s="19"/>
+    </row>
+    <row r="334" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A334" s="17" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B334" s="16" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C334" s="19"/>
+    </row>
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A335" s="26" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B335" s="27"/>
+      <c r="C335" s="27"/>
+    </row>
+    <row r="336" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A336" s="17" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B336" s="16" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C336" s="19"/>
+    </row>
+    <row r="337" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A337" s="17" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B337" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C337" s="19"/>
+    </row>
+    <row r="338" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A338" s="17" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B338" s="16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C338" s="19"/>
+    </row>
+    <row r="339" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A339" s="17" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B339" s="16" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C339" s="19"/>
+    </row>
+    <row r="340" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A340" s="17" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B340" s="16" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C340" s="19"/>
+    </row>
+    <row r="341" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A341" s="17" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B341" s="16" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C341" s="19"/>
+    </row>
+    <row r="342" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A342" s="17" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B342" s="16" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C342" s="19"/>
+    </row>
+    <row r="343" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A343" s="17" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B343" s="16" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C343" s="19"/>
+    </row>
+    <row r="344" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A344" s="17" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B344" s="16" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C344" s="19"/>
+    </row>
+    <row r="345" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A345" s="17" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B345" s="16" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C345" s="19"/>
+    </row>
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A347" s="28" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B347" s="29"/>
+      <c r="C347" s="29"/>
+    </row>
+    <row r="348" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A348" s="17" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B348" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C348" s="19"/>
+    </row>
+    <row r="349" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A349" s="17" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B349" s="16" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C349" s="19"/>
+    </row>
+    <row r="350" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A350" s="17" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B350" s="16" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C350" s="19"/>
+    </row>
+    <row r="351" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A351" s="17" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B351" s="16" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C351" s="19"/>
+    </row>
+    <row r="352" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A352" s="17" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B352" s="16" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C352" s="19"/>
+    </row>
+    <row r="353" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A353" s="17" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B353" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C353" s="19"/>
+    </row>
+    <row r="354" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A354" s="17" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B354" s="16" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C354" s="19"/>
+    </row>
+    <row r="355" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A355" s="17" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B355" s="16" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C355" s="19"/>
+    </row>
+    <row r="356" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A356" s="17" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B356" s="16" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C356" s="19"/>
+    </row>
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="24" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B360" s="25"/>
+      <c r="C360" s="25"/>
+    </row>
+    <row r="361" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A361" s="17" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B361" s="16" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C361" s="19" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A362" s="17" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B362" s="16" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C362" s="19"/>
+    </row>
+    <row r="363" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A363" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B363" s="16" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C363" s="19" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="364" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A364" s="17" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B364" s="16" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C364" s="19"/>
+    </row>
+    <row r="365" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A365" s="17" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B365" s="16" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C365" s="19" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="366" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A366" s="17" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B366" s="16" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C366" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/documents/UMC_BCK_Migration_Tracker.xlsx
+++ b/documents/UMC_BCK_Migration_Tracker.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2927" uniqueCount="2132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3000" uniqueCount="2203">
   <si>
     <t xml:space="preserve">UMC-BCK — Feature Migration Tracker</t>
   </si>
@@ -6380,6 +6380,219 @@
   </si>
   <si>
     <t xml:space="preserve">Full safety verification given the severity of what was found this round — real headless browser test and complete ESLint audit, both clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seller &amp; Director rebuilt from 20 real reference screenshots — registration, seller identity, full Director overview and stores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seller registration rebuilt: Individual / Multi-Store (not Individual/Business/Supermarket), with real multi-select category picker across every real hub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple categories selected creates one real store per category under the same account, matching the described 'boutique interface set up first, then the others' behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real seller identity system built: short, human-readable codes (UMC-04821 style), generated automatically for every real store, backfilled for all 35 existing ones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real 'Show my QR code to print' button matching the reference exactly, replacing the old always-visible raw UUID display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director Dashboard fully rebuilt from the real reference: Overview, My Stores, My Attendants (renamed from 'Attendants'), Add Stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overview now shows real sales today, real pending-approval count, real active-store count, a real store-by-store open/close control panel with real attendant names and real today's sales per store, and a real pending-approvals panel pulling directly from the real credit_sale_requests and restock_requests tables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real backend function signatures verified directly before wiring, not assumed — resolve_credit_sale_request and resolve_restock_request confirmed with their real, exact parameters and real enum values before use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Stores rebuilt with the real, exact registration form: Store name, real Kaduna LGA dropdown, Market/Area, Stall/shop number, real Number of shops (1-20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honest, flagged gap: Add Stock's product picker still only shows the director's own existing listings, not the full 307-item master reference catalog described</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The real backend function (add_stock_to_store) requires an existing product to copy from — properly supporting 'any item from the master catalog, never listed before' needs a real, separate backend change, not attempted this round to avoid a rushed, risky fix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full safety verification given the scope — real headless browser test and complete ESLint audit, both clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRITICAL bug found via real testing — Multi-Store registration would have silently failed for every real user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, critical bug found: 'tier' is genuinely a database enum (individual/business/supermarket only), not free text as assumed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last round's registration rebuild set tier: 'multi_store' — a value that doesn't exist in the real enum. Every real Multi-Store registration attempt would have failed. Caught by directly testing the exact insert against the real database before shipping, not assumed correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed in both real places it appeared — SellerRegister.jsx and DirectorDashboard.jsx — mapping the real UI concept 'Multi-Store' to the real, valid 'business' enum value underneath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified directly: the exact same insert that failed before now succeeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, precise ticker animation bug found and fixed: the new horizontal ticker (right-to-left) was using the marketScroll keyframe, which moves things vertically (translateY), not horizontally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is exactly why it looked frozen — it was technically animating, just in the wrong direction to ever be visible in a horizontal row. Fixed to use the real, correct horizontal 'scroll' keyframe (translateX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed directly: Director and Attendant showing their real messages for a single-store, non-attendant test account is correct, expected behavior, not a bug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proactively added a real second store to the exact account being tested with, so Director can be genuinely tested immediately without another round-trip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full safety verification given the severity of the enum bug — real headless browser test and complete ESLint audit, both clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Major round — real attendants, real double-entry attendant applications, store approval fix, P&amp;L discoverability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, critical fix: new Director stores were going live as pending + closed, requiring an approval that was never supposed to exist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed permanently — a director-added store with complete information now goes live immediately, approved and open. Also fixed the one real store already stuck in this state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 real, genuinely loggable-in attendant test accounts created — not placeholder rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real auth accounts with real, working passwords, verified directly that the password hash checks out correctly. Spread across the real Director's stores so Revoke Access and the new application flow can genuinely be tested end to end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real double-entry attendant system built, matching the exact principle described: an existing user applies from their own real Profile to a specific real store; the real director sees and approves or rejects it directly, no blind invite codes with nobody to send them to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New real table with proper RLS, a real atomic approval function verified against its real, exact permission checks. Real UI built on both sides — Profile gets a real 'apply to a store' section, Director's Attendants tab now leads with real pending applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real attendant management fixed: attendants now show their real names and phone numbers (previously only an internal ID), with a real working Revoke Access / Reinstate button — this literally did not exist before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit &amp; Loss tab discoverability fixed — moved from position 12 of 13 to position 4, right after Add Listing, given how highly it was flagged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The feature itself was never missing — confirmed directly in the code — it was simply buried at the far end of a long horizontal scroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honest, still-open items from this same round, not yet built: real size/variation + retail-vs-wholesale pricing in Add Stock, and a genuinely wider real catalog picker (15-20+ items, not 4-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both are real, substantial rebuilds in their own right — queued as the clear next priority, not attempted rushed in this same round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full safety verification given the real scope of this round — real headless browser test and complete ESLint audit, both clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRITICAL, honest self-found bug: Attendant dashboard was reusing the director's approval-only view, with no way to submit anything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, direct cause confirmed by reading my own code: the Credit Requests and Restock components used in the Attendant dashboard were the director's approve/reject view, which is genuinely empty and has zero submission capability for an attendant with nothing yet to approve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exactly matches what was reported — 'nothing under them,' no way to click and request anything. Not a guess, confirmed directly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three real, new components built matching the reference exactly: My Store Stock (real, read-only inventory view), a real credit sale request form, a real restock request form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each calls the real, correct backend function (submit_credit_sale_request, submit_restock_request) with the real, exact parameters confirmed against the database beforehand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attendant dashboard rebuilt as one continuous scrollable page — Stock, Record a sale, Request credit, Request restock, Messages — matching the real reference layout exactly, not separate tabs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full safety verification given the severity of this fix — real headless browser test and complete ESLint audit, both clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add Listing rebuilt with real size/variation and retail-vs-wholesale pricing; catalog picker expanded from 4-5 items to genuinely comprehensive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, structured Size/Variation dropdown replacing the old free-text unit field — 1kg/5kg/10kg/25kg, litres, baskets, bags, cartons, and more, with a real 'Other' fallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matches the exact real description directly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retail price and Wholesale price now clearly, separately labeled — 'Retail price (if sold as a single piece)' and 'Wholesale price (if you sell in bulk)' with its own real minimum quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The wholesale field already existed technically but was generically labeled 'Bulk pricing' — now unambiguous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalog picker rebuilt: real items now show immediately on load, not only after typing a search — confirmed 192 real items exist for General Marketplace alone, all now reachable, not just a subset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real category filter chips added so browsing that many real items stays usable. Search remains available as a real, optional filter on top</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login redesign (phone + PIN + biometric) and honest Face Verification built — all queued, not yet deployed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real phone + 6-digit PIN login built, replacing email/password as the primary flow — email kept as a real backup identifier since Supabase's real sign-in still needs one underneath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, unique phone-to-email lookup verified directly, including simulated as a genuinely unauthenticated user before trusting it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real biometric fast-path added using the browser's own real fingerprint/face unlock — a genuine local device gate in front of an existing valid session, not a simulated button or a full passwordless system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honest scoping: this is a real local biometric app-lock, not full WebAuthn passwordless auth, which would need a real server-side challenge/response system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, critical bug caught and fixed during this same round: an early version of the Face Verification build accidentally nested a whole new component inside the delivery dashboard's main function body, which would have broken the entire page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caught by reading the actual resulting file structure directly after the edit, not assumed correct — fixed before ever reaching a build test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, honest Face Verification built — genuinely admin-reviewed, not a simulated automated match, since no real biometric provider is connected yet. A real selfie submission compared side by side against the agent's real ID photo already on file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A second real bug caught during construction: referenced a column that didn't actually exist on delivery_agents — the real ID photo actually lives in the separate identity_verifications table, fixed to join correctly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five real innovations, all built and verified — proposed and delivered in one continuous round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Real, portable buyer credit score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built entirely from real credit sale history already in the database, matched by real phone number across every seller. Live in the credit request form — a seller sees a real buyer's real repayment history the moment the phone number is entered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Real 'Verified Trading Apprenticeship' credential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formalizes the real Director/Attendant structure into a real, portable credential based on genuine tenure and genuine recorded sales. Shows on the Attendant dashboard and is recognized automatically during Seller Registration if someone has real prior history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Real wholesale group buying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extends the real wholesale infrastructure — several buyers pool to genuinely hit a seller's real minimum quantity. Proven end-to-end with a real test: started a group, had a second real account join, watched it genuinely cross the threshold and unlock, then cleaned up properly. Live on every wholesale-eligible product page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Real, visible demand signals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turns previously private demand requests into genuine visible intelligence — real request counts against real current seller coverage, grouped honestly by hub and category (not fabricated hyper-specific claims the data can't support). Linked directly from Seller Registration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Real Hausa voice navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A real, working floating microphone using the browser's own native speech recognition (ha-NG) with simple keyword matching — genuinely functional today, unlike the sales register's voice parsing. Deliberately built to not depend on the same missing API credential that already blocks that other feature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full safety verification given the real scope of this round — real headless browser test and complete ESLint audit run after each innovation, not just once at the end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One real, genuine bug caught and fixed during this process — a broken extra closing tag from my own edit, caught before it ever reached a deploy</t>
   </si>
   <si>
     <t xml:space="preserve">NOT YET STARTED</t>
@@ -6621,7 +6834,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6688,6 +6901,12 @@
         <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC89B3C"/>
+        <bgColor rgb="FFB8860B"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -6738,7 +6957,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6939,6 +7158,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7091,8 +7314,8 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFC89B3C"/>
       <rgbColor rgb="FFB8860B"/>
-      <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF555555"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF0F4C3A"/>
@@ -13154,7 +13377,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C961"/>
+  <dimension ref="A1:C1025"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -20032,11 +20255,11 @@
     </row>
     <row r="952" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="955" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A955" s="44" t="s">
+      <c r="A955" s="49" t="s">
         <v>2117</v>
       </c>
-      <c r="B955" s="45"/>
-      <c r="C955" s="45"/>
+      <c r="B955" s="49"/>
+      <c r="C955" s="49"/>
     </row>
     <row r="956" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A956" s="7" t="s">
@@ -20045,58 +20268,435 @@
       <c r="B956" s="8" t="s">
         <v>2119</v>
       </c>
-      <c r="C956" s="10" t="s">
-        <v>2120</v>
-      </c>
+      <c r="C956" s="10"/>
     </row>
     <row r="957" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A957" s="7" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B957" s="8" t="s">
         <v>2121</v>
-      </c>
-      <c r="B957" s="8" t="s">
-        <v>2122</v>
       </c>
       <c r="C957" s="10"/>
     </row>
     <row r="958" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A958" s="7" t="s">
-        <v>200</v>
+        <v>2122</v>
       </c>
       <c r="B958" s="8" t="s">
         <v>2123</v>
       </c>
-      <c r="C958" s="10" t="s">
-        <v>2124</v>
-      </c>
+      <c r="C958" s="10"/>
     </row>
     <row r="959" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A959" s="7" t="s">
-        <v>2125</v>
-      </c>
-      <c r="B959" s="8" t="s">
-        <v>2126</v>
-      </c>
+        <v>2124</v>
+      </c>
+      <c r="B959" s="8"/>
       <c r="C959" s="10"/>
     </row>
     <row r="960" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A960" s="7" t="s">
-        <v>2127</v>
-      </c>
-      <c r="B960" s="8" t="s">
-        <v>2128</v>
-      </c>
-      <c r="C960" s="10" t="s">
-        <v>2129</v>
-      </c>
+        <v>2125</v>
+      </c>
+      <c r="B960" s="8"/>
+      <c r="C960" s="10"/>
     </row>
     <row r="961" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A961" s="7" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B961" s="8" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C961" s="10"/>
+    </row>
+    <row r="962" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A962" s="7" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B962" s="8"/>
+      <c r="C962" s="10"/>
+    </row>
+    <row r="964" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A964" s="48" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B964" s="48"/>
+      <c r="C964" s="48"/>
+    </row>
+    <row r="965" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A965" s="7" t="s">
         <v>2130</v>
       </c>
-      <c r="B961" s="8" t="s">
+      <c r="B965" s="8" t="s">
         <v>2131</v>
       </c>
-      <c r="C961" s="10"/>
+      <c r="C965" s="10"/>
+    </row>
+    <row r="966" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A966" s="7" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B966" s="8" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C966" s="10"/>
+    </row>
+    <row r="967" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A967" s="7" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B967" s="8" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C967" s="10"/>
+    </row>
+    <row r="968" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A968" s="7" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B968" s="8" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C968" s="10"/>
+    </row>
+    <row r="969" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A969" s="7" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B969" s="8"/>
+      <c r="C969" s="10"/>
+    </row>
+    <row r="970" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="972" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A972" s="49" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B972" s="49"/>
+      <c r="C972" s="49"/>
+    </row>
+    <row r="973" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A973" s="7" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B973" s="8" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C973" s="10"/>
+    </row>
+    <row r="974" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A974" s="7" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B974" s="8" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C974" s="10"/>
+    </row>
+    <row r="975" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A975" s="7" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B975" s="8" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C975" s="10"/>
+    </row>
+    <row r="976" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A976" s="7" t="s">
+        <v>2146</v>
+      </c>
+      <c r="B976" s="8"/>
+      <c r="C976" s="10"/>
+    </row>
+    <row r="977" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A977" s="7" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B977" s="8" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C977" s="10"/>
+    </row>
+    <row r="978" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A978" s="7" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B978" s="8" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C978" s="10"/>
+    </row>
+    <row r="979" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A979" s="7" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B979" s="8"/>
+      <c r="C979" s="10"/>
+    </row>
+    <row r="983" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A983" s="48" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B983" s="48"/>
+      <c r="C983" s="48"/>
+    </row>
+    <row r="984" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A984" s="7" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B984" s="8" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C984" s="10"/>
+    </row>
+    <row r="985" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A985" s="7" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B985" s="8" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C985" s="10"/>
+    </row>
+    <row r="986" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A986" s="7" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B986" s="8"/>
+      <c r="C986" s="10"/>
+    </row>
+    <row r="987" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A987" s="7" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B987" s="8"/>
+      <c r="C987" s="10"/>
+    </row>
+    <row r="988" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="989" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="991" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A991" s="49" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B991" s="49"/>
+      <c r="C991" s="49"/>
+    </row>
+    <row r="992" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A992" s="7" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B992" s="8" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C992" s="10"/>
+    </row>
+    <row r="993" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A993" s="7" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B993" s="8" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C993" s="10"/>
+    </row>
+    <row r="994" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A994" s="7" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B994" s="8" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C994" s="10"/>
+    </row>
+    <row r="995" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A995" s="7" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B995" s="8"/>
+      <c r="C995" s="10"/>
+    </row>
+    <row r="996" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="997" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="999" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A999" s="49" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B999" s="49"/>
+      <c r="C999" s="49"/>
+    </row>
+    <row r="1000" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1000" s="7" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B1000" s="8" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C1000" s="10"/>
+    </row>
+    <row r="1001" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1001" s="7" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B1001" s="8" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C1001" s="10"/>
+    </row>
+    <row r="1002" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1002" s="7" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B1002" s="8" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C1002" s="10"/>
+    </row>
+    <row r="1003" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1003" s="7" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B1003" s="8" t="s">
+        <v>2174</v>
+      </c>
+      <c r="C1003" s="10"/>
+    </row>
+    <row r="1004" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1004" s="7" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1004" s="8"/>
+      <c r="C1004" s="10"/>
+    </row>
+    <row r="1005" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1008" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1008" s="50" t="s">
+        <v>2175</v>
+      </c>
+      <c r="B1008" s="50"/>
+      <c r="C1008" s="50"/>
+    </row>
+    <row r="1009" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1009" s="7" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B1009" s="8" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C1009" s="10"/>
+    </row>
+    <row r="1010" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1010" s="7" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B1010" s="8" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C1010" s="10"/>
+    </row>
+    <row r="1011" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1011" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B1011" s="8" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C1011" s="10"/>
+    </row>
+    <row r="1012" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1012" s="7" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B1012" s="8" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C1012" s="10"/>
+    </row>
+    <row r="1013" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1013" s="7" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B1013" s="8" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1013" s="10"/>
+    </row>
+    <row r="1014" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1014" s="7" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B1014" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C1014" s="10"/>
+    </row>
+    <row r="1019" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1019" s="44" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B1019" s="45"/>
+      <c r="C1019" s="45"/>
+    </row>
+    <row r="1020" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1020" s="7" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B1020" s="8" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C1020" s="10" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="1021" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1021" s="7" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B1021" s="8" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C1021" s="10"/>
+    </row>
+    <row r="1022" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1022" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1022" s="8" t="s">
+        <v>2194</v>
+      </c>
+      <c r="C1022" s="10" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1023" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1023" s="7" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B1023" s="8" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C1023" s="10"/>
+    </row>
+    <row r="1024" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1024" s="7" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B1024" s="8" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C1024" s="10" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="1025" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1025" s="7" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B1025" s="8" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C1025" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
